--- a/Documents/BOM/TG21_Slave_Device_Led_1.xlsx
+++ b/Documents/BOM/TG21_Slave_Device_Led_1.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\DELL\Documents\GitHub\Altium-cp1\TG21_Slave_Device_Led_1\Documents\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61257D00-6AD0-46AE-9055-74F4C4E02F55}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85E56C17-7E4F-460E-8B41-BD89A9A8C4EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{45624977-85C6-4A2D-899C-38304A4548ED}"/>
   </bookViews>
@@ -1254,8 +1254,8 @@
         <v>1</v>
       </c>
       <c r="I9" s="18">
-        <f>H9*4</f>
-        <v>4</v>
+        <f>H9*5</f>
+        <v>5</v>
       </c>
       <c r="J9" s="16" t="s">
         <v>136</v>
@@ -1297,8 +1297,8 @@
         <v>2</v>
       </c>
       <c r="I10" s="18">
-        <f>H10*4</f>
-        <v>8</v>
+        <f t="shared" ref="I10:I27" si="0">H10*5</f>
+        <v>10</v>
       </c>
       <c r="J10" s="16" t="s">
         <v>136</v>
@@ -1340,8 +1340,8 @@
         <v>6</v>
       </c>
       <c r="I11" s="18">
-        <f t="shared" ref="I11:I27" si="0">H11*4</f>
-        <v>24</v>
+        <f t="shared" si="0"/>
+        <v>30</v>
       </c>
       <c r="J11" s="16" t="s">
         <v>136</v>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="I12" s="18">
         <f t="shared" si="0"/>
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="J12" s="16" t="s">
         <v>136</v>
@@ -1427,7 +1427,7 @@
       </c>
       <c r="I13" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J13" s="16" t="s">
         <v>136</v>
@@ -1470,7 +1470,7 @@
       </c>
       <c r="I14" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J14" s="16" t="s">
         <v>136</v>
@@ -1513,7 +1513,7 @@
       </c>
       <c r="I15" s="18">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J15" s="16" t="s">
         <v>136</v>
@@ -1556,7 +1556,7 @@
       </c>
       <c r="I16" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J16" s="16" t="s">
         <v>136</v>
@@ -1599,7 +1599,7 @@
       </c>
       <c r="I17" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J17" s="16" t="s">
         <v>136</v>
@@ -1642,7 +1642,7 @@
       </c>
       <c r="I18" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J18" s="16" t="s">
         <v>136</v>
@@ -1685,7 +1685,7 @@
       </c>
       <c r="I19" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J19" s="16" t="s">
         <v>136</v>
@@ -1728,7 +1728,7 @@
       </c>
       <c r="I20" s="18">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J20" s="16" t="s">
         <v>136</v>
@@ -1771,7 +1771,7 @@
       </c>
       <c r="I21" s="18">
         <f t="shared" si="0"/>
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="J21" s="16" t="s">
         <v>136</v>
@@ -1814,7 +1814,7 @@
       </c>
       <c r="I22" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J22" s="16" t="s">
         <v>136</v>
@@ -1857,7 +1857,7 @@
       </c>
       <c r="I23" s="18">
         <f t="shared" si="0"/>
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="J23" s="16" t="s">
         <v>136</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="I24" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J24" s="16" t="s">
         <v>136</v>
@@ -1943,7 +1943,7 @@
       </c>
       <c r="I25" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J25" s="16" t="s">
         <v>136</v>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="I26" s="18">
         <f t="shared" si="0"/>
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J26" s="16" t="s">
         <v>136</v>
@@ -2029,7 +2029,7 @@
       </c>
       <c r="I27" s="18">
         <f t="shared" si="0"/>
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="J27" s="16" t="s">
         <v>136</v>
